--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544387</v>
+        <v>122544123</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770306</v>
+        <v>770552</v>
       </c>
       <c r="R2" t="n">
-        <v>7111082</v>
+        <v>7110954</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544124</v>
+        <v>122544387</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -792,38 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770421</v>
+        <v>770306</v>
       </c>
       <c r="R3" t="n">
-        <v>7110891</v>
+        <v>7111082</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544108</v>
+        <v>122544350</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>56585</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -898,20 +908,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>102612</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -919,9 +934,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770557</v>
+        <v>770377</v>
       </c>
       <c r="R4" t="n">
-        <v>7110971</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544350</v>
+        <v>122544124</v>
       </c>
       <c r="B5" t="n">
-        <v>56581</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,26 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770377</v>
+        <v>770421</v>
       </c>
       <c r="R5" t="n">
-        <v>7111032</v>
+        <v>7110891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544123</v>
+        <v>122544108</v>
       </c>
       <c r="B6" t="n">
-        <v>57532</v>
+        <v>56593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,30 +1138,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1150,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770552</v>
+        <v>770557</v>
       </c>
       <c r="R6" t="n">
-        <v>7110954</v>
+        <v>7110971</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544387</v>
+        <v>122544350</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>56585</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +806,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770306</v>
+        <v>770377</v>
       </c>
       <c r="R3" t="n">
-        <v>7111082</v>
+        <v>7111032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544350</v>
+        <v>122544108</v>
       </c>
       <c r="B4" t="n">
-        <v>56585</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -934,9 +943,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -945,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770377</v>
+        <v>770557</v>
       </c>
       <c r="R4" t="n">
-        <v>7111032</v>
+        <v>7110971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544124</v>
+        <v>122544387</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770421</v>
+        <v>770306</v>
       </c>
       <c r="R5" t="n">
-        <v>7110891</v>
+        <v>7111082</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544108</v>
+        <v>122544124</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,35 +1138,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770557</v>
+        <v>770421</v>
       </c>
       <c r="R6" t="n">
-        <v>7110971</v>
+        <v>7110891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544108</v>
+        <v>122544124</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770557</v>
+        <v>770421</v>
       </c>
       <c r="R4" t="n">
-        <v>7110971</v>
+        <v>7110891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544124</v>
+        <v>122544108</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>56593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,35 +1138,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770421</v>
+        <v>770557</v>
       </c>
       <c r="R6" t="n">
-        <v>7110891</v>
+        <v>7110971</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544123</v>
+        <v>122544108</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>56593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770552</v>
+        <v>770557</v>
       </c>
       <c r="R2" t="n">
-        <v>7110954</v>
+        <v>7110971</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544350</v>
+        <v>122544387</v>
       </c>
       <c r="B3" t="n">
-        <v>56585</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,43 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770377</v>
+        <v>770306</v>
       </c>
       <c r="R3" t="n">
-        <v>7111032</v>
+        <v>7111082</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544124</v>
+        <v>122544350</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>56585</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +912,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770421</v>
+        <v>770377</v>
       </c>
       <c r="R4" t="n">
-        <v>7110891</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544387</v>
+        <v>122544124</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1027,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770306</v>
+        <v>770421</v>
       </c>
       <c r="R5" t="n">
-        <v>7111082</v>
+        <v>7110891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544108</v>
+        <v>122544123</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,35 +1138,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770557</v>
+        <v>770552</v>
       </c>
       <c r="R6" t="n">
-        <v>7110971</v>
+        <v>7110954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544108</v>
+        <v>122544350</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>56586</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770557</v>
+        <v>770377</v>
       </c>
       <c r="R2" t="n">
-        <v>7110971</v>
+        <v>7111032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544387</v>
+        <v>122544108</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770306</v>
+        <v>770557</v>
       </c>
       <c r="R3" t="n">
-        <v>7111082</v>
+        <v>7110971</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544350</v>
+        <v>122544124</v>
       </c>
       <c r="B4" t="n">
-        <v>56585</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +921,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -945,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770377</v>
+        <v>770421</v>
       </c>
       <c r="R4" t="n">
-        <v>7111032</v>
+        <v>7110891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544124</v>
+        <v>122544123</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770421</v>
+        <v>770552</v>
       </c>
       <c r="R5" t="n">
-        <v>7110891</v>
+        <v>7110954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544123</v>
+        <v>122544387</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,43 +1151,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770552</v>
+        <v>770306</v>
       </c>
       <c r="R6" t="n">
-        <v>7110954</v>
+        <v>7111082</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544350</v>
+        <v>122544124</v>
       </c>
       <c r="B2" t="n">
-        <v>56586</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770377</v>
+        <v>770421</v>
       </c>
       <c r="R2" t="n">
-        <v>7111032</v>
+        <v>7110891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544108</v>
+        <v>122544350</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
+        <v>56586</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,9 +828,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770557</v>
+        <v>770377</v>
       </c>
       <c r="R3" t="n">
-        <v>7110971</v>
+        <v>7111032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544124</v>
+        <v>122544387</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,43 +921,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770421</v>
+        <v>770306</v>
       </c>
       <c r="R4" t="n">
-        <v>7110891</v>
+        <v>7111082</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1135,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544387</v>
+        <v>122544108</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,38 +1138,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770306</v>
+        <v>770557</v>
       </c>
       <c r="R6" t="n">
-        <v>7111082</v>
+        <v>7110971</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544124</v>
+        <v>122544350</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>56586</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770421</v>
+        <v>770377</v>
       </c>
       <c r="R2" t="n">
-        <v>7110891</v>
+        <v>7111032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544350</v>
+        <v>122544124</v>
       </c>
       <c r="B3" t="n">
-        <v>56586</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770377</v>
+        <v>770421</v>
       </c>
       <c r="R3" t="n">
-        <v>7111032</v>
+        <v>7110891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544387</v>
+        <v>122544123</v>
       </c>
       <c r="B4" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,34 +921,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770306</v>
+        <v>770552</v>
       </c>
       <c r="R4" t="n">
-        <v>7111082</v>
+        <v>7110954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544123</v>
+        <v>122544108</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1032,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770552</v>
+        <v>770557</v>
       </c>
       <c r="R5" t="n">
-        <v>7110954</v>
+        <v>7110971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544108</v>
+        <v>122544387</v>
       </c>
       <c r="B6" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,47 +1147,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770557</v>
+        <v>770306</v>
       </c>
       <c r="R6" t="n">
-        <v>7110971</v>
+        <v>7111082</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544350</v>
+        <v>122544124</v>
       </c>
       <c r="B2" t="n">
-        <v>56586</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770377</v>
+        <v>770421</v>
       </c>
       <c r="R2" t="n">
-        <v>7111032</v>
+        <v>7110891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544124</v>
+        <v>122544123</v>
       </c>
       <c r="B3" t="n">
         <v>57537</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770421</v>
+        <v>770552</v>
       </c>
       <c r="R3" t="n">
-        <v>7110891</v>
+        <v>7110954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544123</v>
+        <v>122544350</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>56586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +921,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770552</v>
+        <v>770377</v>
       </c>
       <c r="R4" t="n">
-        <v>7110954</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544124</v>
+        <v>122544350</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>56586</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770421</v>
+        <v>770377</v>
       </c>
       <c r="R2" t="n">
-        <v>7110891</v>
+        <v>7111032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544123</v>
+        <v>122544124</v>
       </c>
       <c r="B3" t="n">
         <v>57537</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770552</v>
+        <v>770421</v>
       </c>
       <c r="R3" t="n">
-        <v>7110954</v>
+        <v>7110891</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544350</v>
+        <v>122544123</v>
       </c>
       <c r="B4" t="n">
-        <v>56586</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +921,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770377</v>
+        <v>770552</v>
       </c>
       <c r="R4" t="n">
-        <v>7111032</v>
+        <v>7110954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544350</v>
+        <v>122544387</v>
       </c>
       <c r="B2" t="n">
-        <v>56586</v>
+        <v>78762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770377</v>
+        <v>770306</v>
       </c>
       <c r="R2" t="n">
-        <v>7111032</v>
+        <v>7111082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544124</v>
+        <v>122544108</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770421</v>
+        <v>770557</v>
       </c>
       <c r="R3" t="n">
-        <v>7110891</v>
+        <v>7110971</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544123</v>
+        <v>122544350</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>56680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,31 +912,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770552</v>
+        <v>770377</v>
       </c>
       <c r="R4" t="n">
-        <v>7110954</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544108</v>
+        <v>122544123</v>
       </c>
       <c r="B5" t="n">
-        <v>56594</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,35 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770557</v>
+        <v>770552</v>
       </c>
       <c r="R5" t="n">
-        <v>7110971</v>
+        <v>7110954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544387</v>
+        <v>122544124</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,34 +1142,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770306</v>
+        <v>770421</v>
       </c>
       <c r="R6" t="n">
-        <v>7111082</v>
+        <v>7110891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122544387</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544350</v>
+        <v>122544123</v>
       </c>
       <c r="B4" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +912,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770377</v>
+        <v>770552</v>
       </c>
       <c r="R4" t="n">
-        <v>7111032</v>
+        <v>7110954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544123</v>
+        <v>122544350</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>56680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,31 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770552</v>
+        <v>770377</v>
       </c>
       <c r="R5" t="n">
-        <v>7110954</v>
+        <v>7111032</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544123</v>
+        <v>122544350</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>56680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +912,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770552</v>
+        <v>770377</v>
       </c>
       <c r="R4" t="n">
-        <v>7110954</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544350</v>
+        <v>122544124</v>
       </c>
       <c r="B5" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,31 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770377</v>
+        <v>770421</v>
       </c>
       <c r="R5" t="n">
-        <v>7111032</v>
+        <v>7110891</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544124</v>
+        <v>122544123</v>
       </c>
       <c r="B6" t="n">
         <v>57631</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770421</v>
+        <v>770552</v>
       </c>
       <c r="R6" t="n">
-        <v>7110891</v>
+        <v>7110954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544108</v>
+        <v>122544350</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>56680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,9 +819,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770557</v>
+        <v>770377</v>
       </c>
       <c r="R3" t="n">
-        <v>7110971</v>
+        <v>7111032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544350</v>
+        <v>122544108</v>
       </c>
       <c r="B4" t="n">
-        <v>56680</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +908,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -934,9 +934,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>770377</v>
+        <v>770557</v>
       </c>
       <c r="R4" t="n">
-        <v>7111032</v>
+        <v>7110971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 42812-2024 artfynd.xlsx
+++ b/artfynd/A 42812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544387</v>
+        <v>122544124</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>770306</v>
+        <v>770421</v>
       </c>
       <c r="R2" t="n">
-        <v>7111082</v>
+        <v>7110891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544350</v>
+        <v>122544123</v>
       </c>
       <c r="B3" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>770377</v>
+        <v>770552</v>
       </c>
       <c r="R3" t="n">
-        <v>7111032</v>
+        <v>7110954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122544124</v>
+        <v>122544387</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>V om Granträsket, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>770421</v>
+        <v>770306</v>
       </c>
       <c r="R5" t="n">
-        <v>7110891</v>
+        <v>7111082</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544123</v>
+        <v>122544350</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>56680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,31 +1142,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>770552</v>
+        <v>770377</v>
       </c>
       <c r="R6" t="n">
-        <v>7110954</v>
+        <v>7111032</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
